--- a/src/MxTwoWaySql/twsmockdata/sample/test1.xlsx
+++ b/src/MxTwoWaySql/twsmockdata/sample/test1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\MxTwoWaySql\src\MxTwoWaySql\mockdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\MxTwoWaySql\src\MxTwoWaySql\twsmockdata\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50398E21-926B-4FD1-8415-CE9E850854B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3ED5F39-8895-4AD9-BBCA-510B4B4B1C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29304" yWindow="-4716" windowWidth="30876" windowHeight="16812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28920" yWindow="-6300" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="26.19921875" bestFit="1" customWidth="1"/>
@@ -514,36 +514,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>62</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="b">
+      <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>999.99</v>
+      </c>
+      <c r="G6">
+        <v>999</v>
       </c>
     </row>
   </sheetData>
